--- a/data/indicadores/08_09_02_02_pbt.xlsx
+++ b/data/indicadores/08_09_02_02_pbt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Prueba_4\Input_indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C713B026-1BEF-4714-8097-BFB35D5EBAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638C4686-E81D-4EC3-AD0B-5DD8A19743FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9432" yWindow="2448" windowWidth="11160" windowHeight="10488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Procesados" sheetId="15" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="506">
   <si>
     <t>Coipasa</t>
   </si>
@@ -1551,9 +1551,6 @@
   </si>
   <si>
     <t>Total Valor Agregado en millones de Bs. 2025 (Preliminar)</t>
-  </si>
-  <si>
-    <t>Total  PIB en millones de Bs. 2025 (Preliminar)</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2368,7 @@
         <v>499</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J1" s="48" t="s">
         <v>494</v>
@@ -2493,7 +2490,7 @@
         <v>246.02</v>
       </c>
       <c r="J3" s="54">
-        <f>(H3/I3)*100</f>
+        <f t="shared" ref="J3:J66" si="1">(H3/I3)*100</f>
         <v>2.6786440126818958</v>
       </c>
       <c r="L3" s="7" t="s">
@@ -2520,7 +2517,7 @@
         <v>107671.22999999992</v>
       </c>
       <c r="R3" s="65">
-        <f t="shared" ref="R3:R12" si="1">100*P3/Q3</f>
+        <f t="shared" ref="R3:R12" si="2">100*P3/Q3</f>
         <v>4.2226414614191778</v>
       </c>
       <c r="S3" s="57"/>
@@ -2556,7 +2553,7 @@
         <v>274.36</v>
       </c>
       <c r="J4" s="54">
-        <f t="shared" ref="J3:J66" si="2">(H4/I4)*100</f>
+        <f t="shared" si="1"/>
         <v>0.98410847062253981</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -2583,7 +2580,7 @@
         <v>65237.36</v>
       </c>
       <c r="R4" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.5917707276934587</v>
       </c>
       <c r="S4" s="57"/>
@@ -2619,7 +2616,7 @@
         <v>227.09</v>
       </c>
       <c r="J5" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.2726231890439914</v>
       </c>
       <c r="L5" s="7" t="s">
@@ -2646,7 +2643,7 @@
         <v>19069.940000000002</v>
       </c>
       <c r="R5" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.9370831790765997</v>
       </c>
       <c r="S5" s="57"/>
@@ -2709,7 +2706,7 @@
         <v>38643.990000000013</v>
       </c>
       <c r="R6" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2328957232418274</v>
       </c>
       <c r="S6" s="57"/>
@@ -2745,7 +2742,7 @@
         <v>257.86</v>
       </c>
       <c r="J7" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8.054758396028852</v>
       </c>
       <c r="L7" s="7" t="s">
@@ -2772,7 +2769,7 @@
         <v>25046.53</v>
       </c>
       <c r="R7" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0803069327367902</v>
       </c>
       <c r="S7" s="57"/>
@@ -2808,7 +2805,7 @@
         <v>221.78</v>
       </c>
       <c r="J8" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.3436739110830553</v>
       </c>
       <c r="L8" s="7" t="s">
@@ -2871,7 +2868,7 @@
         <v>248</v>
       </c>
       <c r="J9" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6048387096774193</v>
       </c>
       <c r="L9" s="7" t="s">
@@ -2898,7 +2895,7 @@
         <v>15450.549999999997</v>
       </c>
       <c r="R9" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.9897964797369672</v>
       </c>
       <c r="S9" s="57"/>
@@ -2934,7 +2931,7 @@
         <v>160.32</v>
       </c>
       <c r="J10" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.601047904191617</v>
       </c>
       <c r="L10" s="7" t="s">
@@ -2997,7 +2994,7 @@
         <v>366.55</v>
       </c>
       <c r="J11" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.7936161505933708</v>
       </c>
       <c r="L11" s="45" t="s">
@@ -3056,7 +3053,7 @@
         <v>184.04</v>
       </c>
       <c r="J12" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.5211910454249078</v>
       </c>
       <c r="L12" s="7" t="s">
@@ -3083,7 +3080,7 @@
         <v>433223.18999999994</v>
       </c>
       <c r="R12" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.8074069857617743</v>
       </c>
       <c r="S12" s="57"/>
@@ -3119,7 +3116,7 @@
         <v>158.84</v>
       </c>
       <c r="J13" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.9390581717451523</v>
       </c>
       <c r="Q13" s="59"/>
@@ -3154,7 +3151,7 @@
         <v>113.16</v>
       </c>
       <c r="J14" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.6850477200424177</v>
       </c>
     </row>
@@ -3187,7 +3184,7 @@
         <v>145.72</v>
       </c>
       <c r="J15" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1048586329947847</v>
       </c>
     </row>
@@ -3220,7 +3217,7 @@
         <v>793.09</v>
       </c>
       <c r="J16" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.7485153009116239</v>
       </c>
     </row>
@@ -3253,7 +3250,7 @@
         <v>319.14999999999998</v>
       </c>
       <c r="J17" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.7953940153532824</v>
       </c>
     </row>
@@ -3286,7 +3283,7 @@
         <v>338.96</v>
       </c>
       <c r="J18" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.2602076941232001</v>
       </c>
     </row>
@@ -3319,7 +3316,7 @@
         <v>212.1</v>
       </c>
       <c r="J19" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4521452145214522</v>
       </c>
     </row>
@@ -3352,7 +3349,7 @@
         <v>444.95</v>
       </c>
       <c r="J20" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.4004944375772554</v>
       </c>
     </row>
@@ -3385,7 +3382,7 @@
         <v>1048.57</v>
       </c>
       <c r="J21" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.67806631889144264</v>
       </c>
     </row>
@@ -3418,7 +3415,7 @@
         <v>228.72</v>
       </c>
       <c r="J22" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1367611052815669</v>
       </c>
     </row>
@@ -3451,7 +3448,7 @@
         <v>302.20999999999998</v>
       </c>
       <c r="J23" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.95628867343899948</v>
       </c>
     </row>
@@ -3484,7 +3481,7 @@
         <v>228.1</v>
       </c>
       <c r="J24" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.9281017097764144</v>
       </c>
     </row>
@@ -3517,7 +3514,7 @@
         <v>89.4</v>
       </c>
       <c r="J25" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.8143176733780759</v>
       </c>
     </row>
@@ -3550,7 +3547,7 @@
         <v>560.59</v>
       </c>
       <c r="J26" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.90440428833907138</v>
       </c>
     </row>
@@ -3583,7 +3580,7 @@
         <v>171.86</v>
       </c>
       <c r="J27" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.82625392761550098</v>
       </c>
     </row>
@@ -3616,7 +3613,7 @@
         <v>359.97</v>
       </c>
       <c r="J28" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5140150568102897</v>
       </c>
     </row>
@@ -3649,7 +3646,7 @@
         <v>2568.9499999999998</v>
       </c>
       <c r="J29" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.9194807216956345E-2</v>
       </c>
     </row>
@@ -3682,7 +3679,7 @@
         <v>654.91</v>
       </c>
       <c r="J30" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.89019865325006498</v>
       </c>
     </row>
@@ -3715,7 +3712,7 @@
         <v>46346.36</v>
       </c>
       <c r="J31" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.1264945078750523</v>
       </c>
     </row>
@@ -3748,7 +3745,7 @@
         <v>594.45000000000005</v>
       </c>
       <c r="J32" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.94877617966187211</v>
       </c>
     </row>
@@ -3781,7 +3778,7 @@
         <v>397.36</v>
       </c>
       <c r="J33" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.7630360378498082</v>
       </c>
     </row>
@@ -3814,7 +3811,7 @@
         <v>484.92</v>
       </c>
       <c r="J34" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.7430504000659903</v>
       </c>
     </row>
@@ -3847,7 +3844,7 @@
         <v>25068.86</v>
       </c>
       <c r="J35" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.8897030020511512</v>
       </c>
     </row>
@@ -3880,7 +3877,7 @@
         <v>1114.75</v>
       </c>
       <c r="J36" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.939896837856022</v>
       </c>
     </row>
@@ -3913,7 +3910,7 @@
         <v>213.86</v>
       </c>
       <c r="J37" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.94921911530908065</v>
       </c>
     </row>
@@ -3946,7 +3943,7 @@
         <v>228.02</v>
       </c>
       <c r="J38" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.8067713358477326</v>
       </c>
     </row>
@@ -3979,7 +3976,7 @@
         <v>195.63</v>
       </c>
       <c r="J39" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8229821602003784</v>
       </c>
     </row>
@@ -4012,7 +4009,7 @@
         <v>129.74</v>
       </c>
       <c r="J40" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.3588715893325114</v>
       </c>
     </row>
@@ -4045,7 +4042,7 @@
         <v>248.06</v>
       </c>
       <c r="J41" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.8259292106748366</v>
       </c>
     </row>
@@ -4078,7 +4075,7 @@
         <v>451.07</v>
       </c>
       <c r="J42" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.84022435542155316</v>
       </c>
     </row>
@@ -4111,7 +4108,7 @@
         <v>223.45</v>
       </c>
       <c r="J43" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.3336316849407026</v>
       </c>
     </row>
@@ -4144,7 +4141,7 @@
         <v>283.05</v>
       </c>
       <c r="J44" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.78431372549019607</v>
       </c>
     </row>
@@ -4177,7 +4174,7 @@
         <v>72.12</v>
       </c>
       <c r="J45" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4420410427065999</v>
       </c>
     </row>
@@ -4210,7 +4207,7 @@
         <v>175.55</v>
       </c>
       <c r="J46" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.70065508402164622</v>
       </c>
     </row>
@@ -4243,7 +4240,7 @@
         <v>133.27000000000001</v>
       </c>
       <c r="J47" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0655061154048173</v>
       </c>
     </row>
@@ -4276,7 +4273,7 @@
         <v>13.89</v>
       </c>
       <c r="J48" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8.135349172066233</v>
       </c>
     </row>
@@ -4309,7 +4306,7 @@
         <v>136.75</v>
       </c>
       <c r="J49" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0383912248628884</v>
       </c>
     </row>
@@ -4342,7 +4339,7 @@
         <v>214.02</v>
       </c>
       <c r="J50" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.2753948229137464</v>
       </c>
     </row>
@@ -4375,7 +4372,7 @@
         <v>304.55</v>
       </c>
       <c r="J51" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0408799868658676</v>
       </c>
     </row>
@@ -4408,7 +4405,7 @@
         <v>491.22</v>
       </c>
       <c r="J52" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.3745775823459957</v>
       </c>
     </row>
@@ -4441,7 +4438,7 @@
         <v>92.01</v>
       </c>
       <c r="J53" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.51081404195196167</v>
       </c>
     </row>
@@ -4474,7 +4471,7 @@
         <v>104.9</v>
       </c>
       <c r="J54" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.3927550047664439</v>
       </c>
     </row>
@@ -4507,7 +4504,7 @@
         <v>209.09</v>
       </c>
       <c r="J55" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.2434836673202927</v>
       </c>
     </row>
@@ -4540,7 +4537,7 @@
         <v>203.18</v>
       </c>
       <c r="J56" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.60537454473865537</v>
       </c>
     </row>
@@ -4573,7 +4570,7 @@
         <v>141.69999999999999</v>
       </c>
       <c r="J57" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.2985179957657025</v>
       </c>
     </row>
@@ -4606,7 +4603,7 @@
         <v>903.59</v>
       </c>
       <c r="J58" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.8606115605529059</v>
       </c>
     </row>
@@ -4639,7 +4636,7 @@
         <v>1257.19</v>
       </c>
       <c r="J59" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0443926534573136</v>
       </c>
     </row>
@@ -4672,7 +4669,7 @@
         <v>954.97</v>
       </c>
       <c r="J60" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.22304365582164884</v>
       </c>
     </row>
@@ -4705,7 +4702,7 @@
         <v>121.59</v>
       </c>
       <c r="J61" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.38654494613043833</v>
       </c>
     </row>
@@ -4738,7 +4735,7 @@
         <v>60.39</v>
       </c>
       <c r="J62" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.61268421924159633</v>
       </c>
     </row>
@@ -4771,7 +4768,7 @@
         <v>519.49</v>
       </c>
       <c r="J63" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.8470230418294862</v>
       </c>
     </row>
@@ -4804,7 +4801,7 @@
         <v>1103.23</v>
       </c>
       <c r="J64" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.5099027401357832</v>
       </c>
     </row>
@@ -4837,7 +4834,7 @@
         <v>422.75</v>
       </c>
       <c r="J65" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.0526315789473684</v>
       </c>
     </row>
@@ -4870,7 +4867,7 @@
         <v>653.32000000000005</v>
       </c>
       <c r="J66" s="54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.2336986469111613</v>
       </c>
     </row>
